--- a/vorlagen/projektrechner-vorlage.xlsx
+++ b/vorlagen/projektrechner-vorlage.xlsx
@@ -599,7 +599,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wohnungsspiegel  je Wohnung eine Zeile — Haus, Zimmer, Fläche, Preis oder Miete</t>
+          <t>Wohnungsspiegel  je Wohnung eine Zeile — Nr., Geschoss, Zimmer, Fläche, Preis oder Miete</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -958,30 +959,35 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Bezeichnung</t>
+          <t>Nr.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>Geschoss</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Zimmer</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Fläche m²</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Preis CHF</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Miete CHF/Monat</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
@@ -1000,20 +1006,23 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>1.1 Erdgeschoss links</t>
+          <t>A 1.1</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="6" t="n">
         <v>850000</v>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1030,20 +1039,23 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>1.2 Erdgeschoss rechts</t>
+          <t>A 1.2</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>1050000</v>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1060,20 +1072,23 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2.1 Erdgeschoss</t>
+          <t>B 2.1</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n">
         <v>1650</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1086,6 +1101,7 @@
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -1096,6 +1112,7 @@
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -1106,6 +1123,7 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -1116,6 +1134,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -1126,6 +1145,7 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1136,6 +1156,7 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -1146,6 +1167,7 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -1156,6 +1178,7 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -1166,6 +1189,7 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1176,6 +1200,7 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1186,6 +1211,7 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1196,6 +1222,7 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1206,6 +1233,7 @@
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1216,6 +1244,7 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1226,6 +1255,7 @@
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1236,6 +1266,7 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1246,6 +1277,7 @@
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1256,6 +1288,7 @@
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1266,6 +1299,7 @@
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1276,6 +1310,7 @@
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1286,6 +1321,7 @@
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1296,6 +1332,7 @@
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1306,6 +1343,7 @@
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1316,6 +1354,7 @@
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1326,6 +1365,7 @@
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1336,6 +1376,7 @@
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1346,6 +1387,7 @@
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1356,6 +1398,7 @@
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1366,6 +1409,7 @@
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1376,6 +1420,7 @@
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1386,6 +1431,7 @@
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1396,6 +1442,7 @@
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1406,6 +1453,7 @@
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1416,6 +1464,7 @@
       <c r="F41" s="6" t="n"/>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1426,6 +1475,7 @@
       <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1436,6 +1486,7 @@
       <c r="F43" s="6" t="n"/>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1446,6 +1497,7 @@
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1456,6 +1508,7 @@
       <c r="F45" s="6" t="n"/>
       <c r="G45" s="6" t="n"/>
       <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -1466,6 +1519,7 @@
       <c r="F46" s="6" t="n"/>
       <c r="G46" s="6" t="n"/>
       <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -1476,6 +1530,7 @@
       <c r="F47" s="6" t="n"/>
       <c r="G47" s="6" t="n"/>
       <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -1486,6 +1541,7 @@
       <c r="F48" s="6" t="n"/>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="6" t="n"/>
+      <c r="I48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -1496,6 +1552,7 @@
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n"/>
       <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -1506,6 +1563,7 @@
       <c r="F50" s="6" t="n"/>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -1516,6 +1574,7 @@
       <c r="F51" s="6" t="n"/>
       <c r="G51" s="6" t="n"/>
       <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -1526,6 +1585,7 @@
       <c r="F52" s="6" t="n"/>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -1536,6 +1596,7 @@
       <c r="F53" s="6" t="n"/>
       <c r="G53" s="6" t="n"/>
       <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -1546,6 +1607,7 @@
       <c r="F54" s="6" t="n"/>
       <c r="G54" s="6" t="n"/>
       <c r="H54" s="6" t="n"/>
+      <c r="I54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -1556,6 +1618,7 @@
       <c r="F55" s="6" t="n"/>
       <c r="G55" s="6" t="n"/>
       <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -1566,6 +1629,7 @@
       <c r="F56" s="6" t="n"/>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="6" t="n"/>
+      <c r="I56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -1576,6 +1640,7 @@
       <c r="F57" s="6" t="n"/>
       <c r="G57" s="6" t="n"/>
       <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -1586,6 +1651,7 @@
       <c r="F58" s="6" t="n"/>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -1596,6 +1662,7 @@
       <c r="F59" s="6" t="n"/>
       <c r="G59" s="6" t="n"/>
       <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -1606,6 +1673,7 @@
       <c r="F60" s="6" t="n"/>
       <c r="G60" s="6" t="n"/>
       <c r="H60" s="6" t="n"/>
+      <c r="I60" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1617,14 +1685,28 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Die drei Zeilen oben sind Beispiele — bitte überschreiben oder löschen.</t>
+          <t>Nr.: die Bezeichnung der Wohnung, z. B. A 1.1 — Text ist erlaubt.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>Geschoss: 0 = Erdgeschoss, 1 = 1. Obergeschoss, -1 = Untergeschoss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
           <t>Anzahl: wie oft diese Wohnung vorkommt. Leer oder 1 = einmal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Die drei Zeilen oben sind Beispiele — bitte überschreiben oder löschen.</t>
         </is>
       </c>
     </row>
